--- a/Data/Home/Context.Humidity.xlsx
+++ b/Data/Home/Context.Humidity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709258347</v>
+        <v>1711860657</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709281498</v>
+        <v>1711886280</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709250888</v>
+        <v>1711937183</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709262164</v>
+        <v>1711967120</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709271316</v>
+        <v>1712023692</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +634,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709312163</v>
+        <v>1712053121</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709343838</v>
+        <v>1712109809</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709353737</v>
+        <v>1712137080</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709363079</v>
+        <v>1712195459</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +766,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709429190</v>
+        <v>1712223781</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709448887</v>
+        <v>1712282270</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +832,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709508534</v>
+        <v>1712312241</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709535024</v>
+        <v>1712377471</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +898,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709596057</v>
+        <v>1712401668</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709621626</v>
+        <v>1712455574</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +964,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709683476</v>
+        <v>1712485097</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1001,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709686256</v>
+        <v>1712549305</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1030,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709706645</v>
+        <v>1712572845</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1063,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709769308</v>
+        <v>1712627968</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1096,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709789708</v>
+        <v>1712658042</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1129,11 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709855071</v>
+        <v>1712714244</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1162,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709875476</v>
+        <v>1712744202</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1195,11 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709880944</v>
+        <v>1712800543</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1228,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709944046</v>
+        <v>1712829322</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709961294</v>
+        <v>1712886403</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1265,10 +1294,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709967507</v>
+        <v>1712916660</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1327,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709977717</v>
+        <v>1712981561</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1360,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1710028299</v>
+        <v>1713006047</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1397,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1710050802</v>
+        <v>1713059545</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1426,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1710114736</v>
+        <v>1713089066</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710136810</v>
+        <v>1713154031</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1492,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710137805</v>
+        <v>1713177464</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1525,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710149047</v>
+        <v>1713196804</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1558,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710212868</v>
+        <v>1713234142</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1591,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
+          <t>Context.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710225439</v>
+        <v>1713264882</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1624,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710233935</v>
+        <v>1713320029</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1657,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710244320</v>
+        <v>1713348410</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1649,10 +1690,11 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710291574</v>
+        <v>1713413249</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1723,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
+          <t>Context.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710302470</v>
+        <v>1713437204</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1756,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710318675</v>
+        <v>1713492011</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1789,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710329723</v>
+        <v>1713521126</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1777,10 +1822,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710374662</v>
+        <v>1713579853</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1855,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
+          <t>Context.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710381196</v>
+        <v>1713610698</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1888,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710398037</v>
+        <v>1713663620</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1921,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710409201</v>
+        <v>1713690918</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1954,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710464139</v>
+        <v>1713750104</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +1987,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
+          <t>Context.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710486330</v>
+        <v>1713778326</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2020,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710552036</v>
+        <v>1713836853</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2053,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
+          <t>Context.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710553708</v>
+        <v>1713865948</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2033,10 +2086,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710569267</v>
+        <v>1713931350</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2119,11 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ExtremelyDry</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710633179</v>
+        <v>1713955774</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2152,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710655821</v>
+        <v>1714017082</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2185,11 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710671831</v>
+        <v>1714017998</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2161,10 +2218,11 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710721970</v>
+        <v>1714041057</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2255,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710739703</v>
+        <v>1714097024</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2284,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710746433</v>
+        <v>1714127476</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2257,10 +2317,11 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710807458</v>
+        <v>1714183191</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2350,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710831589</v>
+        <v>1714213898</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2383,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710837644</v>
+        <v>1714270978</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2353,10 +2416,11 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710891463</v>
+        <v>1714300788</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,1030 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1710899095</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1710917168</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1710950653</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>1710979378</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>1710987035</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1711002884</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>1711037535</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>1711066047</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>1711088587</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>1711152568</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>1711169236</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1711175421</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1711186294</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>1711241586</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>1711265241</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>1711267635</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>1711278970</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1711326684</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>1711347907</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>1711352383</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>1711361388</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>1711418982</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>1711449434</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>1711451225</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1711465549</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>1711506060</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>1711512458</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1711538879</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>1711555638</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>1711591441</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ComfortableHumidity</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1711594981</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: Moist</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Humidity_Change</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>1711623743</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
